--- a/FES04N.xlsx
+++ b/FES04N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
   <si>
     <t/>
   </si>
@@ -41,6 +41,18 @@
   </si>
   <si>
     <t>5</t>
+  </si>
+  <si>
+    <t>20143686</t>
+  </si>
+  <si>
+    <t>KURMA KHALAS AKRAM</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>,(E-1B)</t>
   </si>
 </sst>
 </file>
@@ -433,7 +445,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -503,6 +515,26 @@
         <v>6</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/FES04N.xlsx
+++ b/FES04N.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="17">
   <si>
     <t/>
   </si>
@@ -28,28 +28,37 @@
     <t>1</t>
   </si>
   <si>
+    <t>PT,(E-1B)</t>
+  </si>
+  <si>
+    <t>20140192</t>
+  </si>
+  <si>
+    <t>KURMA SAYER BRARI250</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>RT,(E-2H)</t>
+  </si>
+  <si>
+    <t>20140218</t>
+  </si>
+  <si>
+    <t>KURMA TUNIS BRARI500</t>
+  </si>
+  <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20113971</t>
-  </si>
-  <si>
-    <t>KURMA MEDJOOL  PCK</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>20143686</t>
   </si>
   <si>
     <t>KURMA KHALAS AKRAM</t>
   </si>
   <si>
-    <t>6</t>
+    <t>4</t>
   </si>
   <si>
     <t>,(E-1B)</t>
@@ -445,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F5"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -489,18 +498,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -509,10 +518,10 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
@@ -532,7 +541,27 @@
         <v>12</v>
       </c>
       <c r="F4" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
         <v>13</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
